--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420668</v>
+        <v>123420666</v>
       </c>
       <c r="B2" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602289</v>
+        <v>602335</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6833981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420669</v>
+        <v>123420668</v>
       </c>
       <c r="B3" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602148</v>
+        <v>602289</v>
       </c>
       <c r="R3" t="n">
-        <v>6833969</v>
+        <v>6833995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420667</v>
+        <v>123420669</v>
       </c>
       <c r="B4" t="n">
-        <v>98285</v>
+        <v>98404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,26 +951,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602319</v>
+        <v>602148</v>
       </c>
       <c r="R4" t="n">
-        <v>6833985</v>
+        <v>6833969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420666</v>
+        <v>123420667</v>
       </c>
       <c r="B6" t="n">
-        <v>98402</v>
+        <v>98287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,14 +1240,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602335</v>
+        <v>602319</v>
       </c>
       <c r="R6" t="n">
-        <v>6833981</v>
+        <v>6833985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420666</v>
+        <v>123420668</v>
       </c>
       <c r="B2" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602335</v>
+        <v>602289</v>
       </c>
       <c r="R2" t="n">
-        <v>6833981</v>
+        <v>6833995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420668</v>
+        <v>123420682</v>
       </c>
       <c r="B3" t="n">
-        <v>98404</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602289</v>
+        <v>602131</v>
       </c>
       <c r="R3" t="n">
-        <v>6833995</v>
+        <v>6833957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420669</v>
+        <v>123420667</v>
       </c>
       <c r="B4" t="n">
-        <v>98404</v>
+        <v>98293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,26 +951,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602148</v>
+        <v>602319</v>
       </c>
       <c r="R4" t="n">
-        <v>6833969</v>
+        <v>6833985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420682</v>
+        <v>123420666</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>98410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,42 +1077,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602131</v>
+        <v>602335</v>
       </c>
       <c r="R5" t="n">
-        <v>6833957</v>
+        <v>6833981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1149,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420667</v>
+        <v>123420669</v>
       </c>
       <c r="B6" t="n">
-        <v>98287</v>
+        <v>98410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,14 +1240,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602319</v>
+        <v>602148</v>
       </c>
       <c r="R6" t="n">
-        <v>6833985</v>
+        <v>6833969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420668</v>
+        <v>123420682</v>
       </c>
       <c r="B2" t="n">
-        <v>98413</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602289</v>
+        <v>602131</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6833957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420666</v>
+        <v>123420667</v>
       </c>
       <c r="B3" t="n">
-        <v>98413</v>
+        <v>98313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,26 +821,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602335</v>
+        <v>602319</v>
       </c>
       <c r="R3" t="n">
-        <v>6833981</v>
+        <v>6833985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420682</v>
+        <v>123420669</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>98430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,42 +947,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602131</v>
+        <v>602148</v>
       </c>
       <c r="R4" t="n">
-        <v>6833957</v>
+        <v>6833969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420667</v>
+        <v>123420668</v>
       </c>
       <c r="B5" t="n">
-        <v>98296</v>
+        <v>98430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602319</v>
+        <v>602289</v>
       </c>
       <c r="R5" t="n">
-        <v>6833985</v>
+        <v>6833995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420669</v>
+        <v>123420666</v>
       </c>
       <c r="B6" t="n">
-        <v>98413</v>
+        <v>98430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602148</v>
+        <v>602335</v>
       </c>
       <c r="R6" t="n">
-        <v>6833969</v>
+        <v>6833981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420682</v>
+        <v>123420668</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>98536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602131</v>
+        <v>602289</v>
       </c>
       <c r="R2" t="n">
-        <v>6833957</v>
+        <v>6833995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420667</v>
+        <v>123420666</v>
       </c>
       <c r="B3" t="n">
-        <v>98313</v>
+        <v>98536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,26 +821,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602319</v>
+        <v>602335</v>
       </c>
       <c r="R3" t="n">
-        <v>6833985</v>
+        <v>6833981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -938,7 +938,7 @@
         <v>123420669</v>
       </c>
       <c r="B4" t="n">
-        <v>98430</v>
+        <v>98536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420668</v>
+        <v>123420682</v>
       </c>
       <c r="B5" t="n">
-        <v>98430</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,21 +1103,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602289</v>
+        <v>602131</v>
       </c>
       <c r="R5" t="n">
-        <v>6833995</v>
+        <v>6833957</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1159,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420666</v>
+        <v>123420667</v>
       </c>
       <c r="B6" t="n">
-        <v>98430</v>
+        <v>98419</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,14 +1240,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602335</v>
+        <v>602319</v>
       </c>
       <c r="R6" t="n">
-        <v>6833981</v>
+        <v>6833985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420668</v>
+        <v>123420669</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98538</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602289</v>
+        <v>602148</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6833969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -808,7 +808,7 @@
         <v>123420666</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
+        <v>98538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420669</v>
+        <v>123420682</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,47 +947,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602148</v>
+        <v>602131</v>
       </c>
       <c r="R4" t="n">
-        <v>6833969</v>
+        <v>6833957</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420682</v>
+        <v>123420667</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>98421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,30 +1077,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602131</v>
+        <v>602319</v>
       </c>
       <c r="R5" t="n">
-        <v>6833957</v>
+        <v>6833985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1149,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420667</v>
+        <v>123420668</v>
       </c>
       <c r="B6" t="n">
-        <v>98419</v>
+        <v>98538</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602319</v>
+        <v>602289</v>
       </c>
       <c r="R6" t="n">
-        <v>6833985</v>
+        <v>6833995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420669</v>
+        <v>123420682</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602148</v>
+        <v>602131</v>
       </c>
       <c r="R2" t="n">
-        <v>6833969</v>
+        <v>6833957</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420666</v>
+        <v>123420668</v>
       </c>
       <c r="B3" t="n">
-        <v>98538</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,14 +850,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602335</v>
+        <v>602289</v>
       </c>
       <c r="R3" t="n">
-        <v>6833981</v>
+        <v>6833995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420682</v>
+        <v>123420669</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,42 +947,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602131</v>
+        <v>602148</v>
       </c>
       <c r="R4" t="n">
-        <v>6833957</v>
+        <v>6833969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420667</v>
+        <v>123420666</v>
       </c>
       <c r="B5" t="n">
-        <v>98421</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602319</v>
+        <v>602335</v>
       </c>
       <c r="R5" t="n">
-        <v>6833985</v>
+        <v>6833981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420668</v>
+        <v>123420667</v>
       </c>
       <c r="B6" t="n">
-        <v>98538</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602289</v>
+        <v>602319</v>
       </c>
       <c r="R6" t="n">
-        <v>6833995</v>
+        <v>6833985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420682</v>
+        <v>123420666</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602131</v>
+        <v>602335</v>
       </c>
       <c r="R2" t="n">
-        <v>6833957</v>
+        <v>6833981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2427</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackhål i sälg</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420668</v>
+        <v>123420682</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602289</v>
+        <v>602131</v>
       </c>
       <c r="R3" t="n">
-        <v>6833995</v>
+        <v>6833957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2427</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hackhål i sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420669</v>
+        <v>123420668</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602148</v>
+        <v>602289</v>
       </c>
       <c r="R4" t="n">
-        <v>6833969</v>
+        <v>6833995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420666</v>
+        <v>123420667</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602335</v>
+        <v>602319</v>
       </c>
       <c r="R5" t="n">
-        <v>6833981</v>
+        <v>6833985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420667</v>
+        <v>123420669</v>
       </c>
       <c r="B6" t="n">
-        <v>97996</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,26 +1211,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1240,14 +1240,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602319</v>
+        <v>602148</v>
       </c>
       <c r="R6" t="n">
-        <v>6833985</v>
+        <v>6833969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420666</v>
+        <v>123420668</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602335</v>
+        <v>602289</v>
       </c>
       <c r="R2" t="n">
-        <v>6833981</v>
+        <v>6833995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -935,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420668</v>
+        <v>123420669</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602289</v>
+        <v>602148</v>
       </c>
       <c r="R4" t="n">
-        <v>6833995</v>
+        <v>6833969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420669</v>
+        <v>123420666</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602148</v>
+        <v>602335</v>
       </c>
       <c r="R6" t="n">
-        <v>6833969</v>
+        <v>6833981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13640-2025 artfynd.xlsx
+++ b/artfynd/A 13640-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420668</v>
+        <v>123420666</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsjöberget, Hls</t>
+          <t>Edsjöberget S om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602289</v>
+        <v>602335</v>
       </c>
       <c r="R2" t="n">
-        <v>6833995</v>
+        <v>6833981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2441</t>
+          <t>2024_2443</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ofir Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420669</v>
+        <v>123420667</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,26 +951,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Edsjöberget S om, Hls</t>
+          <t>Edsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602148</v>
+        <v>602319</v>
       </c>
       <c r="R4" t="n">
-        <v>6833969</v>
+        <v>6833985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2440</t>
+          <t>2024_2442</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Ofir Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420667</v>
+        <v>123420668</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,26 +1081,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602319</v>
+        <v>602289</v>
       </c>
       <c r="R5" t="n">
-        <v>6833985</v>
+        <v>6833995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2442</t>
+          <t>2024_2441</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420666</v>
+        <v>123420669</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602335</v>
+        <v>602148</v>
       </c>
       <c r="R6" t="n">
-        <v>6833981</v>
+        <v>6833969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2443</t>
+          <t>2024_2440</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
